--- a/Scripts/FCE Updates- Communication Board-1.xlsx
+++ b/Scripts/FCE Updates- Communication Board-1.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meihua.jin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/AskMira/Scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5DE581-84E7-4DCF-9465-8DAB251A5BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7E1566-7FF0-884F-BAE2-C420B5C0D589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conmmunication Board" sheetId="1" r:id="rId1"/>
-    <sheet name="Archive" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conmmunication Board'!$A$1:$F$1</definedName>
@@ -560,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -604,13 +603,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -898,18 +895,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="16" customWidth="1"/>
     <col min="2" max="2" width="16" style="6" customWidth="1"/>
-    <col min="3" max="3" width="17.1796875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="43" style="10" customWidth="1"/>
     <col min="5" max="5" width="113" style="9" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.1796875" style="7"/>
+    <col min="6" max="6" width="17.1640625" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -922,16 +919,16 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="17" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
-        <v>45450</v>
+        <v>45815</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>6</v>
@@ -949,9 +946,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="18" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" s="17" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
-        <v>45536</v>
+        <v>45901</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>6</v>
@@ -969,9 +966,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
-        <v>45537</v>
+        <v>45902</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>6</v>
@@ -989,9 +986,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="19" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
-        <v>45580</v>
+        <v>45945</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>6</v>
@@ -1009,9 +1006,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="20" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" s="18" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
-        <v>45636</v>
+        <v>46001</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>6</v>
@@ -1029,7 +1026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="19" customFormat="1" ht="140.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>45667</v>
       </c>
@@ -1049,7 +1046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="19" customFormat="1" ht="175.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>45674</v>
       </c>
@@ -1069,7 +1066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="20" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" s="18" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>45675</v>
       </c>
@@ -1089,7 +1086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="21" customFormat="1" ht="273.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" s="19" customFormat="1" ht="273.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>45698</v>
       </c>
@@ -1102,14 +1099,14 @@
       <c r="D10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>37</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="22" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" s="20" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>45715</v>
       </c>
@@ -1129,7 +1126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="23" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" s="21" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>45716</v>
       </c>
@@ -1149,7 +1146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="19" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>45717</v>
       </c>
@@ -1169,7 +1166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="19" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
         <v>45718</v>
       </c>
@@ -1189,26 +1186,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:6" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:6" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1216,7 +1199,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="16"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1224,9 +1207,9 @@
       <c r="E21" s="9"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="16"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1234,7 +1217,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1242,7 +1225,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1250,9 +1233,9 @@
       <c r="E26" s="9"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
@@ -1260,13 +1243,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32779FC9-B88D-4874-AD65-438E9766C56E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>